--- a/public/template_siswa.xlsx
+++ b/public/template_siswa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SIMPEL-5\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A43DD4-6FE0-4942-94B0-D8B2DA511159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487A9AE5-9C76-408F-9559-8877B6242E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B5C1236F-2DC1-4DEB-9CB8-AC0626038A09}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>nama</t>
   </si>
@@ -51,31 +51,25 @@
     <t>semester</t>
   </si>
   <si>
-    <t>Manajemen Informatika</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
-    <t>mahasiswa1@gmail.com</t>
-  </si>
-  <si>
-    <t>Teknologi Rekayasa Perangkat Lunak</t>
-  </si>
-  <si>
-    <t>5A - MI</t>
-  </si>
-  <si>
-    <t>7A - TRPL</t>
-  </si>
-  <si>
-    <t>mahasiswa2@gmail.com</t>
-  </si>
-  <si>
-    <t>Nama siswa 2</t>
-  </si>
-  <si>
-    <t>Nama siswa 1</t>
+    <t>siswa5@gmail.com</t>
+  </si>
+  <si>
+    <t>siswa6@gmail.com</t>
+  </si>
+  <si>
+    <t>Siswa 5</t>
+  </si>
+  <si>
+    <t>Siswa 6</t>
+  </si>
+  <si>
+    <t>Multimedia</t>
+  </si>
+  <si>
+    <t>11 MM 1</t>
   </si>
 </sst>
 </file>
@@ -487,47 +481,47 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2">
         <v>1234500</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2">
         <v>1234400</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
